--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487051_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487051_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.6504</v>
+        <v>7.8779</v>
       </c>
       <c r="E2" t="n">
-        <v>5.5907</v>
+        <v>6.7111</v>
       </c>
       <c r="F2" t="n">
-        <v>1.0597</v>
+        <v>1.1668</v>
       </c>
       <c r="G2" t="n">
         <v>10.1432</v>
@@ -610,13 +610,13 @@
         <v>2.3161</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.9909</v>
+        <v>-0.7635</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.4726</v>
+        <v>-0.3523</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.5183</v>
+        <v>-0.4112</v>
       </c>
       <c r="V2" t="n">
         <v>0.0422</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.806</v>
+        <v>4.7203</v>
       </c>
       <c r="E3" t="n">
-        <v>4.7169</v>
+        <v>3.6936</v>
       </c>
       <c r="F3" t="n">
-        <v>1.0892</v>
+        <v>1.0267</v>
       </c>
       <c r="G3" t="n">
         <v>2.7831</v>
@@ -688,13 +688,13 @@
         <v>1.5441</v>
       </c>
       <c r="S3" t="n">
-        <v>1.5018</v>
+        <v>0.4161</v>
       </c>
       <c r="T3" t="n">
-        <v>1.2573</v>
+        <v>0.234</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2445</v>
+        <v>0.1821</v>
       </c>
       <c r="V3" t="n">
         <v>0.9421</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.0314</v>
+        <v>3.2317</v>
       </c>
       <c r="E4" t="n">
-        <v>2.9627</v>
+        <v>2.9221</v>
       </c>
       <c r="F4" t="n">
-        <v>0.06859999999999999</v>
+        <v>0.3096</v>
       </c>
       <c r="G4" t="n">
         <v>3.6618</v>
@@ -766,13 +766,13 @@
         <v>1.5441</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.5532</v>
+        <v>-0.353</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0185</v>
+        <v>-0.0591</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.5348000000000001</v>
+        <v>-0.2938</v>
       </c>
       <c r="V4" t="n">
         <v>-0.6562</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9567</v>
+        <v>0.5611</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.5081</v>
+        <v>-0.4486</v>
       </c>
       <c r="F5" t="n">
-        <v>1.4648</v>
+        <v>1.0097</v>
       </c>
       <c r="G5" t="n">
         <v>-0.7732</v>
@@ -844,13 +844,13 @@
         <v>0.965</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1738</v>
+        <v>-0.2218</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2842</v>
+        <v>-0.2247</v>
       </c>
       <c r="U5" t="n">
-        <v>0.458</v>
+        <v>0.0029</v>
       </c>
       <c r="V5" t="n">
         <v>1.5561</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.2036</v>
+        <v>0.0294</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.1127</v>
+        <v>0.1471</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.09089999999999999</v>
+        <v>-0.1177</v>
       </c>
       <c r="G6" t="n">
         <v>-0.5995</v>
@@ -922,13 +922,13 @@
         <v>0.772</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.4184</v>
+        <v>-0.1854</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5208</v>
+        <v>-0.2611</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1024</v>
+        <v>0.0757</v>
       </c>
       <c r="V6" t="n">
         <v>0.0422</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.2366</v>
+        <v>-0.9500999999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.4335</v>
+        <v>-1.1737</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1969</v>
+        <v>0.2236</v>
       </c>
       <c r="G7" t="n">
         <v>-1.1209</v>
@@ -1000,13 +1000,13 @@
         <v>0.193</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3087</v>
+        <v>-0.0221</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.119</v>
+        <v>0.1408</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1897</v>
+        <v>-0.1629</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.5423</v>
+        <v>-1.0951</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.3249</v>
+        <v>-2.0652</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7827</v>
+        <v>0.97</v>
       </c>
       <c r="G8" t="n">
         <v>-0.1277</v>
@@ -1078,13 +1078,13 @@
         <v>0.772</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.8705000000000001</v>
+        <v>-0.4234</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6544</v>
+        <v>-0.3946</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2162</v>
+        <v>-0.0288</v>
       </c>
       <c r="V8" t="n">
         <v>0.614</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.4112</v>
+        <v>-2.4167</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.3928</v>
+        <v>-3.7731</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9816</v>
+        <v>1.3563</v>
       </c>
       <c r="G9" t="n">
         <v>-0.0741</v>
@@ -1156,13 +1156,13 @@
         <v>1.5441</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.9981</v>
+        <v>-0.0036</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6411</v>
+        <v>-0.0214</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.357</v>
+        <v>0.0178</v>
       </c>
       <c r="V9" t="n">
         <v>0.9421</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>O. HERNANDEZ HERNANDEZ</t>
+          <t>J. OTERO GONZALEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.4702</v>
+        <v>-3.6679</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.4696</v>
+        <v>-5.5093</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9994</v>
+        <v>1.8414</v>
       </c>
       <c r="G10" t="n">
-        <v>-5.8501</v>
+        <v>-2.1419</v>
       </c>
       <c r="H10" t="n">
-        <v>-6.6676</v>
+        <v>-0.9324</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8175</v>
+        <v>-1.2096</v>
       </c>
       <c r="J10" t="n">
-        <v>-5.4162</v>
+        <v>-2.5563</v>
       </c>
       <c r="K10" t="n">
-        <v>-5.579</v>
+        <v>-0.8384</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1628</v>
+        <v>-1.7179</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.4339</v>
+        <v>0.4144</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.0886</v>
+        <v>-0.094</v>
       </c>
       <c r="O10" t="n">
-        <v>0.6546999999999999</v>
+        <v>0.5084</v>
       </c>
       <c r="P10" t="n">
-        <v>0.386</v>
+        <v>-1.3511</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.965</v>
+        <v>-2.8951</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3511</v>
+        <v>1.5441</v>
       </c>
       <c r="S10" t="n">
-        <v>2.2798</v>
+        <v>-0.7889</v>
       </c>
       <c r="T10" t="n">
-        <v>1.9116</v>
+        <v>-0.6296</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3681</v>
+        <v>-0.1593</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.2859</v>
+        <v>0.614</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.5717</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.2859</v>
+        <v>0.0422</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. OTERO GONZALEZ</t>
+          <t>O. HERNANDEZ HERNANDEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.0675</v>
+        <v>-4.8404</v>
       </c>
       <c r="E11" t="n">
-        <v>-6.0695</v>
+        <v>-5.6525</v>
       </c>
       <c r="F11" t="n">
-        <v>2.002</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.1419</v>
+        <v>-5.8501</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.9324</v>
+        <v>-6.6676</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.2096</v>
+        <v>0.8175</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.5563</v>
+        <v>-5.4162</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.8384</v>
+        <v>-5.579</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.7179</v>
+        <v>0.1628</v>
       </c>
       <c r="M11" t="n">
-        <v>0.4144</v>
+        <v>-0.4339</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.094</v>
+        <v>-1.0886</v>
       </c>
       <c r="O11" t="n">
-        <v>0.5084</v>
+        <v>0.6546999999999999</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.3511</v>
+        <v>0.386</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.8951</v>
+        <v>-0.965</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5441</v>
+        <v>1.3511</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.1885</v>
+        <v>0.9095</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.1898</v>
+        <v>0.7288</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0013</v>
+        <v>0.1807</v>
       </c>
       <c r="V11" t="n">
-        <v>0.614</v>
+        <v>-0.2859</v>
       </c>
       <c r="W11" t="n">
-        <v>0.5717</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0.0422</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>2.513100000000002</v>
+        <v>3.450200000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>-6.040800000000001</v>
+        <v>-5.1485</v>
       </c>
       <c r="F12" t="n">
-        <v>8.554</v>
+        <v>8.5984</v>
       </c>
       <c r="G12" t="n">
         <v>5.900700000000001</v>
@@ -1390,13 +1390,13 @@
         <v>12.5456</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.3729</v>
+        <v>-1.4361</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.7315</v>
+        <v>-0.8392000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.6416999999999999</v>
+        <v>-0.5968</v>
       </c>
       <c r="V12" t="n">
         <v>3.8106</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.1844</v>
+        <v>4.1072</v>
       </c>
       <c r="E13" t="n">
-        <v>3.1755</v>
+        <v>1.4731</v>
       </c>
       <c r="F13" t="n">
-        <v>3.0089</v>
+        <v>2.6341</v>
       </c>
       <c r="G13" t="n">
         <v>2.6108</v>
@@ -1468,13 +1468,13 @@
         <v>2.5091</v>
       </c>
       <c r="S13" t="n">
-        <v>3.4913</v>
+        <v>1.4142</v>
       </c>
       <c r="T13" t="n">
-        <v>2.5184</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>0.9729</v>
+        <v>0.5981</v>
       </c>
       <c r="V13" t="n">
         <v>1.4333</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.4443</v>
+        <v>2.8727</v>
       </c>
       <c r="E14" t="n">
         <v>-0.3467</v>
       </c>
       <c r="F14" t="n">
-        <v>2.7911</v>
+        <v>3.2194</v>
       </c>
       <c r="G14" t="n">
         <v>-0.7664</v>
@@ -1546,13 +1546,13 @@
         <v>2.5091</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.1176</v>
+        <v>0.3107</v>
       </c>
       <c r="T14" t="n">
         <v>-0.152</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0344</v>
+        <v>0.4627</v>
       </c>
       <c r="V14" t="n">
         <v>0.8193</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.5642</v>
+        <v>0.8619</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.3082</v>
+        <v>-1.6087</v>
       </c>
       <c r="F15" t="n">
-        <v>2.8724</v>
+        <v>2.4706</v>
       </c>
       <c r="G15" t="n">
         <v>-0.8829</v>
@@ -1624,13 +1624,13 @@
         <v>1.7371</v>
       </c>
       <c r="S15" t="n">
-        <v>1.7979</v>
+        <v>1.0956</v>
       </c>
       <c r="T15" t="n">
-        <v>0.6941000000000001</v>
+        <v>0.3937</v>
       </c>
       <c r="U15" t="n">
-        <v>1.1038</v>
+        <v>0.7019</v>
       </c>
       <c r="V15" t="n">
         <v>-0.1228</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.09909999999999999</v>
+        <v>0.5431</v>
       </c>
       <c r="E16" t="n">
         <v>1.9854</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.0844</v>
+        <v>-1.4423</v>
       </c>
       <c r="G16" t="n">
         <v>2.3294</v>
@@ -1702,13 +1702,13 @@
         <v>2.7021</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.3166</v>
+        <v>0.3255</v>
       </c>
       <c r="T16" t="n">
         <v>0.3372</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.6536999999999999</v>
+        <v>-0.0116</v>
       </c>
       <c r="V16" t="n">
         <v>-3.8489</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.2282</v>
+        <v>-0.1013</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0414</v>
+        <v>0.1415</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.2696</v>
+        <v>-0.2428</v>
       </c>
       <c r="G17" t="n">
         <v>-0.4391</v>
@@ -1780,13 +1780,13 @@
         <v>0.193</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0178</v>
+        <v>0.1448</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>0.1001</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0178</v>
+        <v>0.0446</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.3863</v>
+        <v>-0.1526</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0207</v>
+        <v>0.1208</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.407</v>
+        <v>-0.2735</v>
       </c>
       <c r="G18" t="n">
         <v>-0.2528</v>
@@ -1858,13 +1858,13 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1335</v>
+        <v>0.1001</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>0.1001</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1335</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.5762</v>
+        <v>-0.2761</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.0795</v>
+        <v>-0.7791</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5033</v>
+        <v>0.503</v>
       </c>
       <c r="G19" t="n">
         <v>-1.1109</v>
@@ -1936,13 +1936,13 @@
         <v>0.965</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4303</v>
+        <v>-0.1302</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5354</v>
+        <v>-0.235</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1051</v>
+        <v>0.1048</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.4238</v>
+        <v>-1.1035</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.4229</v>
+        <v>-1.0223</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.0009</v>
+        <v>-0.08119999999999999</v>
       </c>
       <c r="G20" t="n">
         <v>-0.9697</v>
@@ -2014,13 +2014,13 @@
         <v>0.772</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2611</v>
+        <v>0.0592</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5354</v>
+        <v>-0.1348</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2743</v>
+        <v>0.194</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.9882</v>
+        <v>-1.9822</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.0155</v>
+        <v>-2.7151</v>
       </c>
       <c r="F21" t="n">
-        <v>1.0273</v>
+        <v>0.7329</v>
       </c>
       <c r="G21" t="n">
         <v>-3.7815</v>
@@ -2092,13 +2092,13 @@
         <v>1.9301</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1368</v>
+        <v>-0.1309</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5816</v>
+        <v>-0.2812</v>
       </c>
       <c r="U21" t="n">
-        <v>0.4448</v>
+        <v>0.1504</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.4924</v>
+        <v>-2.1047</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.3318</v>
+        <v>-1.1315</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.1606</v>
+        <v>-0.9732</v>
       </c>
       <c r="G22" t="n">
         <v>-0.8754999999999999</v>
@@ -2170,13 +2170,13 @@
         <v>1.9301</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.6326000000000001</v>
+        <v>-0.2449</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3437</v>
+        <v>-0.1434</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2889</v>
+        <v>-0.1015</v>
       </c>
       <c r="V22" t="n">
         <v>-0.9843</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.512</v>
+        <v>-4.5099</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.2723</v>
+        <v>-4.6714</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.2397</v>
+        <v>0.1615</v>
       </c>
       <c r="G23" t="n">
         <v>-1.7622</v>
@@ -2248,13 +2248,13 @@
         <v>2.1231</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.9056</v>
+        <v>0.0965</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.7601</v>
+        <v>-0.1593</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1455</v>
+        <v>0.2558</v>
       </c>
       <c r="V23" t="n">
         <v>-1.1071</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.513299999999999</v>
+        <v>-1.845399999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>-8.553899999999999</v>
+        <v>-8.554</v>
       </c>
       <c r="F24" t="n">
-        <v>6.040800000000002</v>
+        <v>6.7085</v>
       </c>
       <c r="G24" t="n">
         <v>-5.9008</v>
@@ -2326,13 +2326,13 @@
         <v>17.3707</v>
       </c>
       <c r="S24" t="n">
-        <v>2.3729</v>
+        <v>3.0406</v>
       </c>
       <c r="T24" t="n">
-        <v>0.6415000000000002</v>
+        <v>0.6413999999999999</v>
       </c>
       <c r="U24" t="n">
-        <v>1.7315</v>
+        <v>2.3992</v>
       </c>
       <c r="V24" t="n">
         <v>-3.810499999999999</v>
